--- a/Assets/Scripts/99.Etc/Document/Unity_MiniProject_WBS_20260819_0902.xlsx
+++ b/Assets/Scripts/99.Etc/Document/Unity_MiniProject_WBS_20260819_0902.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MiniProject_01\Assets\Scripts\99.Etc\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D57718-D22D-4654-B9F2-105465272E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07631122-23D6-4716-9D0E-FB29BF2AB241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1503,7 +1503,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="3">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>10</v>
